--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="502">
   <si>
     <t>Filename</t>
   </si>
@@ -808,706 +808,718 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9926,0.0013,0.0019,0.0006</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9850,0.0020,0.0047,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0009,0.9999</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.2985,0.0000,0.0000,0.9482</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9970,0.0016,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0022,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.1710,0.0037,0.8305,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.0009,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.5326,0.0002,0.6418,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.1247,0.8864,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.9986,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9825,0.0004,0.0084,0.0005</t>
+  </si>
+  <si>
+    <t>0.9658,0.0026,0.0219,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.0005,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0008,0.9942,0.0018</t>
+  </si>
+  <si>
+    <t>0.1797,0.0002,0.8963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9985,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0293</t>
+  </si>
+  <si>
+    <t>0.2657,0.5973,0.0180,0.0002</t>
+  </si>
+  <si>
+    <t>0.9902,0.0081,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0004,0.9974,0.0069</t>
+  </si>
+  <si>
+    <t>0.0010,0.9961,0.0040,0.0000</t>
+  </si>
+  <si>
+    <t>0.9238,0.0426,0.0039,0.0050</t>
+  </si>
+  <si>
+    <t>0.0662,0.0043,0.9390,0.0022</t>
+  </si>
+  <si>
+    <t>0.0166,0.9827,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.0041,0.9875,0.0071,0.0024</t>
+  </si>
+  <si>
+    <t>0.0099,0.6459,0.2812,0.0054</t>
+  </si>
+  <si>
+    <t>0.0037,0.0185,0.9302,0.0172</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9977,0.0004</t>
+  </si>
+  <si>
+    <t>0.0065,0.0001,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0051,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.9953,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9521,0.0047,0.5355</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0324,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0236,0.0010,0.9722,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0004,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0039,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9891,0.0030,0.0053,0.0012</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9997,0.0008</t>
+  </si>
+  <si>
+    <t>0.9682,0.0225,0.0041,0.0025</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9508,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0019,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0866,0.0049,0.9266,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0008,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9555,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9945,0.7311,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.3303,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9254,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0110,0.9980</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9880,0.0011,0.0002,0.0044</t>
-  </si>
-  <si>
-    <t>0.0034,0.0000,0.0000,0.9994</t>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.8763,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9922,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9985,0.0677,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9003,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9863,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.0852,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9951,0.0060,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0029,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0016,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9915,0.0039,0.0009,0.0011</t>
-  </si>
-  <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9671,0.0035,0.0183,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.2001,0.0005,0.8533,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0006,0.9969,0.0007</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.1707,0.8418,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9567,0.0002,0.0286,0.0008</t>
-  </si>
-  <si>
-    <t>0.1059,0.0032,0.8742,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.1116,0.0013,0.8746,0.0021</t>
-  </si>
-  <si>
-    <t>0.1649,0.0001,0.8991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9994,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.0327,0.9673,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9936,0.0030,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0039</t>
-  </si>
-  <si>
-    <t>0.0033,0.9904,0.0048,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0704,0.9204,0.0056,0.0009</t>
-  </si>
-  <si>
-    <t>0.0066,0.9799,0.0175,0.0035</t>
-  </si>
-  <si>
-    <t>0.0158,0.9360,0.0400,0.0035</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9989,0.0017</t>
-  </si>
-  <si>
-    <t>0.0161,0.0004,0.9794,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0162,0.0006,0.9846,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.9916,0.0060,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9608,0.0007,0.8873</t>
-  </si>
-  <si>
-    <t>0.0003,0.9991,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0440,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0134,0.0001,0.9881,0.0002</t>
-  </si>
-  <si>
-    <t>0.0163,0.0001,0.9883,0.0001</t>
-  </si>
-  <si>
-    <t>0.0124,0.0003,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0035,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9909,0.0085,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0017,0.9994,0.0006</t>
-  </si>
-  <si>
-    <t>0.9975,0.0007,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9949,0.9856,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0063,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.9975,0.0004,0.0000</t>
+    <t>0.9991,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.0613,0.9837,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1186,0.0001,0.8741,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.9992,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9969,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9962,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5746,0.4607,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.9754,0.0016,0.0112,0.0007</t>
+  </si>
+  <si>
+    <t>0.7658,0.0021,0.2677,0.0002</t>
+  </si>
+  <si>
+    <t>0.2042,0.0567,0.3943,0.0054</t>
+  </si>
+  <si>
+    <t>0.8994,0.0032,0.0723,0.0007</t>
+  </si>
+  <si>
+    <t>0.0041,0.0031,0.0034,0.9922</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.2153,0.0082,0.7841,0.0001</t>
-  </si>
-  <si>
-    <t>0.5225,0.0234,0.4185,0.0017</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9935,0.2291,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.5516,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9762,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0066,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0002,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.6445,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9904,0.8453,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.7205,0.9903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9716,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9938,0.1847,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0033,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0030,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0008,0.9972,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0164,0.0002,0.9887,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.9966,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.9932,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4910,0.5895,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0470,0.0040,0.9466,0.0010</t>
-  </si>
-  <si>
-    <t>0.5180,0.0008,0.5497,0.0004</t>
-  </si>
-  <si>
-    <t>0.6535,0.1515,0.0200,0.0015</t>
-  </si>
-  <si>
-    <t>0.8324,0.0016,0.1585,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.0026,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0005,0.0196</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.5904,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9980,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.7629,0.2419,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.5681,0.4417,0.0049,0.0007</t>
+    <t>0.0000,0.9999,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.5892,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9987,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9687,0.0309,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.0575,0.8863,0.0209,0.0025</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.8686,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.1849,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.0058,0.9872,0.0003</t>
+  </si>
+  <si>
+    <t>0.9480,0.0015,0.0581,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.0001,0.9923,0.0002</t>
+  </si>
+  <si>
+    <t>0.7095,0.0012,0.3113,0.0005</t>
+  </si>
+  <si>
+    <t>0.6529,0.0001,0.0001,0.6298</t>
+  </si>
+  <si>
+    <t>0.0000,0.9937,0.9675,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0059,0.9886,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1473,0.8471,0.0050,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0170,0.0000,0.0002,0.9950</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.0435,0.0524,0.9488,0.0018</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9509,0.0012,0.0140,0.0109</t>
+  </si>
+  <si>
+    <t>0.8393,0.1950,0.0010,0.0006</t>
   </si>
   <si>
     <t>0.9993,0.0001,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9979,0.0004,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9933,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9909,0.9816,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0029,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0176,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.8939,0.0039,0.0990,0.0002</t>
-  </si>
-  <si>
-    <t>0.9058,0.0002,0.1350,0.0000</t>
-  </si>
-  <si>
-    <t>0.5955,0.0117,0.1230,0.0206</t>
-  </si>
-  <si>
-    <t>0.0460,0.0000,0.0000,0.9914</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9836,0.9518,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.9947,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.9962,0.0002,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.7957,0.2020,0.0047,0.0010</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.1620,0.0000,0.0010,0.9001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.2414,0.0226,0.7816,0.0017</t>
-  </si>
-  <si>
-    <t>0.9900,0.0001,0.0005,0.0072</t>
-  </si>
-  <si>
-    <t>0.9760,0.0038,0.0114,0.0034</t>
-  </si>
-  <si>
-    <t>0.7213,0.3797,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9939,0.0039,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9898,0.0063,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.4636,0.3584,0.0201,0.0006</t>
-  </si>
-  <si>
-    <t>0.9330,0.0354,0.0140,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0004,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9960,0.0005,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0024,0.0005,0.0019</t>
+    <t>0.9825,0.0123,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.0436,0.9320,0.0094,0.0003</t>
+  </si>
+  <si>
+    <t>0.0247,0.0299,0.9239,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0011,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9864,0.0055,0.0011,0.0037</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.3343,0.6567,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.7921,0.1477,0.0189,0.0003</t>
+  </si>
+  <si>
+    <t>0.9390,0.0620,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.1145,0.8848,0.0090,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0077,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9939,0.0029,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9460,0.0778,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9904,0.0026,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9993,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0134,0.0002,0.9921,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0015,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0157,0.0393,0.8110,0.0048</t>
+  </si>
+  <si>
+    <t>0.0056,0.0005,0.9937,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0069,0.9860,0.0006</t>
+  </si>
+  <si>
+    <t>0.0214,0.0057,0.9627,0.0001</t>
+  </si>
+  <si>
+    <t>0.0253,0.0454,0.8756,0.0008</t>
+  </si>
+  <si>
+    <t>0.8655,0.0022,0.1225,0.0002</t>
+  </si>
+  <si>
+    <t>0.9683,0.0009,0.0239,0.0002</t>
+  </si>
+  <si>
+    <t>0.4568,0.0126,0.3718,0.0013</t>
+  </si>
+  <si>
+    <t>0.0404,0.9727,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9971,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0179,0.9753,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0473,0.9599,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0376,0.9659,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.5729,0.4365,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9029,0.0017,0.0563,0.0084</t>
+  </si>
+  <si>
+    <t>0.9655,0.0003,0.0334,0.0002</t>
+  </si>
+  <si>
+    <t>0.9737,0.0005,0.0190,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0012</t>
+  </si>
+  <si>
+    <t>0.0010,0.0061,0.9954,0.0016</t>
+  </si>
+  <si>
+    <t>0.0020,0.3900,0.9426,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.0005,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0043,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0025,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0037,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0002,0.0002</t>
   </si>
   <si>
     <t>0.9993,0.0001,0.0001,0.0002</t>
   </si>
   <si>
-    <t>0.9977,0.0005,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9265,0.0990,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.1204,0.8545,0.0070,0.0003</t>
-  </si>
-  <si>
-    <t>0.9907,0.0070,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.8131,0.0114,0.1565,0.0004</t>
-  </si>
-  <si>
-    <t>0.9861,0.0185,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9981,0.0008,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.7512,0.2981,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0012,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9882,0.0044,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0016,0.9962,0.0023</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0088,0.0002,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0189,0.0331,0.8553,0.0013</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.9570,0.0033,0.0201,0.0005</t>
-  </si>
-  <si>
-    <t>0.1989,0.1487,0.3248,0.0006</t>
-  </si>
-  <si>
-    <t>0.0395,0.0146,0.9149,0.0006</t>
-  </si>
-  <si>
-    <t>0.9926,0.0006,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.9764,0.0027,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.0258,0.0002,0.9800,0.0003</t>
-  </si>
-  <si>
-    <t>0.0317,0.9712,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.9963,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0673,0.9218,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.0149,0.9851,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.9946,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.2199,0.2647,0.0666,0.0064</t>
-  </si>
-  <si>
-    <t>0.9949,0.0001,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.7096,0.0018,0.1582,0.0219</t>
-  </si>
-  <si>
-    <t>0.9625,0.0019,0.0212,0.0005</t>
-  </si>
-  <si>
-    <t>0.9301,0.0016,0.0446,0.0019</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9984,0.0017</t>
-  </si>
-  <si>
-    <t>0.0050,0.0178,0.9658,0.0032</t>
-  </si>
-  <si>
-    <t>0.0078,0.6395,0.7341,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0005,0.9966,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0026,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.9926,0.0052,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0031,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9982,0.0020,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0013,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0038,0.0058,0.9938,0.0019</t>
-  </si>
-  <si>
-    <t>0.0092,0.7482,0.1897,0.0020</t>
-  </si>
-  <si>
-    <t>0.9943,0.0001,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.0052,0.0013,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0049,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0229,0.9975,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0012,0.9952,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0015,0.9947,0.0010</t>
-  </si>
-  <si>
-    <t>0.0011,0.0699,0.9928,0.0005</t>
-  </si>
-  <si>
-    <t>0.9926,0.0001,0.0063,0.0000</t>
-  </si>
-  <si>
-    <t>0.9445,0.0001,0.0701,0.0001</t>
-  </si>
-  <si>
-    <t>0.9068,0.0002,0.0913,0.0006</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9866,0.0118,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9971,0.0030,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.0024,0.9799,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0056,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0113,0.0033,0.9735,0.0014</t>
-  </si>
-  <si>
-    <t>0.0034,0.0019,0.9898,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0015,0.9921,0.0062</t>
-  </si>
-  <si>
-    <t>0.0358,0.0023,0.9604,0.0005</t>
-  </si>
-  <si>
-    <t>0.0154,0.0003,0.9729,0.0028</t>
-  </si>
-  <si>
-    <t>0.7951,0.0000,0.0004,0.3154</t>
-  </si>
-  <si>
-    <t>0.0003,0.0034,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0453,0.0001,0.0015,0.9839</t>
-  </si>
-  <si>
-    <t>0.8961,0.0098,0.0123,0.0261</t>
+    <t>0.0002,0.0142,0.9991,0.0019</t>
+  </si>
+  <si>
+    <t>0.0118,0.6902,0.1585,0.0028</t>
+  </si>
+  <si>
+    <t>0.9919,0.0001,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0175,0.9975,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1114,0.0126,0.7890,0.0005</t>
+  </si>
+  <si>
+    <t>0.0987,0.0001,0.9550,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.0006,0.9932,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0124,0.9968,0.0008</t>
+  </si>
+  <si>
+    <t>0.9048,0.0001,0.1347,0.0000</t>
+  </si>
+  <si>
+    <t>0.0971,0.0003,0.9178,0.0003</t>
+  </si>
+  <si>
+    <t>0.9821,0.0004,0.0114,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0042,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0356,0.0037,0.9424,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0021,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0039,0.0095,0.9750,0.0014</t>
+  </si>
+  <si>
+    <t>0.0062,0.0031,0.9801,0.0035</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0082,0.0018,0.9483,0.0772</t>
+  </si>
+  <si>
+    <t>0.0605,0.0029,0.9204,0.0024</t>
+  </si>
+  <si>
+    <t>0.0807,0.0007,0.8760,0.0073</t>
+  </si>
+  <si>
+    <t>0.9699,0.0000,0.0003,0.0341</t>
+  </si>
+  <si>
+    <t>0.0004,0.0127,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0020,0.0001,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.2689,0.0286,0.0012,0.5871</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1905,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1907,7 +1919,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1921,7 +1933,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,7 +1947,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1949,7 +1961,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1963,7 +1975,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1977,7 +1989,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1991,7 +2003,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2005,7 +2017,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2019,7 +2031,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2033,7 +2045,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2047,7 +2059,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,10 +2070,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2075,7 +2087,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2086,10 +2098,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2103,7 +2115,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2117,7 +2129,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2131,7 +2143,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2145,7 +2157,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2159,7 +2171,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2173,7 +2185,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2187,7 +2199,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2201,7 +2213,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,10 +2224,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2229,7 +2241,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2243,7 +2255,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2257,7 +2269,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2271,7 +2283,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2285,7 +2297,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2299,7 +2311,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2313,7 +2325,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2327,7 +2339,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2341,7 +2353,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2355,7 +2367,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2366,10 +2378,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2383,7 +2395,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2397,7 +2409,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2411,7 +2423,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2425,7 +2437,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2439,7 +2451,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2453,7 +2465,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2467,7 +2479,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2481,7 +2493,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2495,7 +2507,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2506,10 +2518,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2523,7 +2535,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2537,7 +2549,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2551,7 +2563,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2565,7 +2577,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2579,7 +2591,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2593,7 +2605,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2607,7 +2619,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2621,7 +2633,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2635,7 +2647,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2649,7 +2661,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2663,7 +2675,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2677,7 +2689,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2691,7 +2703,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2705,7 +2717,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2719,7 +2731,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2733,7 +2745,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2747,7 +2759,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2761,7 +2773,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2775,7 +2787,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2789,7 +2801,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2803,7 +2815,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2817,7 +2829,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2831,7 +2843,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2845,7 +2857,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2859,7 +2871,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2873,7 +2885,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2887,7 +2899,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2898,10 +2910,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2912,10 +2924,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2929,7 +2941,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2943,7 +2955,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2957,7 +2969,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2971,7 +2983,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2985,7 +2997,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2999,7 +3011,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3013,7 +3025,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3027,7 +3039,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3041,7 +3053,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3052,10 +3064,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3069,7 +3081,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3083,7 +3095,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3097,7 +3109,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3111,7 +3123,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3125,7 +3137,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3139,7 +3151,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3153,7 +3165,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3167,7 +3179,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3181,7 +3193,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3195,7 +3207,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3209,7 +3221,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3223,7 +3235,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3237,7 +3249,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3251,7 +3263,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3265,7 +3277,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3279,7 +3291,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3293,7 +3305,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3307,7 +3319,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3321,7 +3333,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3335,7 +3347,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3349,7 +3361,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3363,7 +3375,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3377,7 +3389,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3391,7 +3403,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3405,7 +3417,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>364</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3419,7 +3431,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3433,7 +3445,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3447,7 +3459,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3461,7 +3473,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3472,10 +3484,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3486,10 +3498,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,10 +3512,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3514,10 +3526,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,7 +3543,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3545,7 +3557,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3559,7 +3571,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3573,7 +3585,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3587,7 +3599,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3601,7 +3613,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3615,7 +3627,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3629,7 +3641,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3640,10 +3652,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3657,7 +3669,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>386</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3671,7 +3683,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3685,7 +3697,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3699,7 +3711,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3713,7 +3725,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3727,7 +3739,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3741,7 +3753,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3755,7 +3767,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3769,7 +3781,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3780,10 +3792,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3797,7 +3809,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3811,7 +3823,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3825,7 +3837,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>269</v>
+        <v>362</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3839,7 +3851,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3850,10 +3862,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3867,7 +3879,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3878,10 +3890,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D144" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3895,7 +3907,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>266</v>
+        <v>343</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3909,7 +3921,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>347</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3923,7 +3935,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>396</v>
+        <v>346</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3937,7 +3949,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3951,7 +3963,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3965,7 +3977,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3979,7 +3991,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3990,10 +4002,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4007,7 +4019,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4021,7 +4033,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4035,7 +4047,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4049,7 +4061,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4063,7 +4075,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4077,7 +4089,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4091,7 +4103,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4105,7 +4117,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4119,7 +4131,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4130,10 +4142,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4144,10 +4156,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D163" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4161,7 +4173,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4175,7 +4187,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4189,7 +4201,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4203,7 +4215,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4217,7 +4229,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4231,7 +4243,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4245,7 +4257,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4259,7 +4271,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4273,7 +4285,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4284,10 +4296,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4298,10 +4310,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4315,7 +4327,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4326,10 +4338,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4343,7 +4355,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4357,7 +4369,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4371,7 +4383,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4385,7 +4397,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4399,7 +4411,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4413,7 +4425,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4427,7 +4439,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>432</v>
+        <v>366</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4441,7 +4453,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4455,7 +4467,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4469,7 +4481,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4483,7 +4495,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>436</v>
+        <v>366</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4497,7 +4509,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>432</v>
+        <v>366</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4511,7 +4523,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4525,7 +4537,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4539,7 +4551,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4550,10 +4562,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4564,10 +4576,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4581,7 +4593,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4595,7 +4607,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4609,7 +4621,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4620,10 +4632,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4637,7 +4649,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4651,7 +4663,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4665,7 +4677,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4679,7 +4691,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4693,7 +4705,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4707,7 +4719,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4721,7 +4733,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>451</v>
+        <v>386</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4735,7 +4747,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4749,7 +4761,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4763,7 +4775,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4777,7 +4789,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4791,7 +4803,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4802,10 +4814,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4819,7 +4831,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4833,7 +4845,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4847,7 +4859,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4861,7 +4873,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4875,7 +4887,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4889,7 +4901,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4903,7 +4915,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4917,7 +4929,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4931,7 +4943,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4945,7 +4957,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>420</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4959,7 +4971,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4973,7 +4985,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4987,7 +4999,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5001,7 +5013,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5015,7 +5027,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5029,7 +5041,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5043,7 +5055,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5057,7 +5069,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5071,7 +5083,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5085,7 +5097,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5099,7 +5111,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5113,7 +5125,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5124,10 +5136,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5141,7 +5153,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5155,7 +5167,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>355</v>
+        <v>484</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5169,7 +5181,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5183,7 +5195,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>482</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5197,7 +5209,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5211,7 +5223,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5225,7 +5237,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5239,7 +5251,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>355</v>
+        <v>488</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5253,7 +5265,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5267,7 +5279,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5281,7 +5293,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5295,7 +5307,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5309,7 +5321,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5323,7 +5335,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5337,7 +5349,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5351,7 +5363,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5365,7 +5377,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5379,7 +5391,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5393,7 +5405,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5407,7 +5419,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5421,7 +5433,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>266</v>
+        <v>343</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5435,7 +5447,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>266</v>
+        <v>343</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5446,10 +5458,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
